--- a/docs/03_test/社員登録テスト項目実施書.xlsx
+++ b/docs/03_test/社員登録テスト項目実施書.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1C3D89-D6A1-43C0-AD1E-9BC8244702BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC118D8-E075-442F-B4F7-9ED8D01171B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="0" windowWidth="14400" windowHeight="7270" xr2:uid="{E0ED0D0A-EE17-460D-84B3-7BD93845960A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E0ED0D0A-EE17-460D-84B3-7BD93845960A}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト項目実施" sheetId="1" r:id="rId1"/>
-    <sheet name="１.氏名空欄" sheetId="5" r:id="rId2"/>
-    <sheet name="２.氏名１文字入力" sheetId="6" r:id="rId3"/>
-    <sheet name="3. 氏名を20文字入力" sheetId="7" r:id="rId4"/>
-    <sheet name="4.部署のみ変更" sheetId="8" r:id="rId5"/>
-    <sheet name="5.氏名21文字入力でDomainException" sheetId="9" r:id="rId6"/>
-    <sheet name="６.Homeから登録まで遷移" sheetId="4" r:id="rId7"/>
-    <sheet name="7.登録後メニューに戻る" sheetId="3" r:id="rId8"/>
-    <sheet name="8.登録後続けて入力" sheetId="2" r:id="rId9"/>
+    <sheet name="追加テスト1.氏名を21文字入力" sheetId="10" r:id="rId2"/>
+    <sheet name="１.氏名空欄" sheetId="5" r:id="rId3"/>
+    <sheet name="２.氏名１文字入力" sheetId="6" r:id="rId4"/>
+    <sheet name="3. 氏名を20文字入力" sheetId="7" r:id="rId5"/>
+    <sheet name="4.部署のみ変更" sheetId="8" r:id="rId6"/>
+    <sheet name="5.氏名21文字入力でDomainException" sheetId="9" r:id="rId7"/>
+    <sheet name="６.Homeから登録まで遷移" sheetId="4" r:id="rId8"/>
+    <sheet name="7.登録後メニューに戻る" sheetId="3" r:id="rId9"/>
+    <sheet name="8.登録後続けて入力" sheetId="2" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -75,10 +76,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DomainExceptionエラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>氏名を１文字入力する。</t>
     <rPh sb="0" eb="2">
       <t>シメイ</t>
@@ -216,22 +213,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員情報の登録を完了しました。</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Home画面</t>
   </si>
   <si>
@@ -392,6 +373,62 @@
     <t>氏名を21文字入力すると、DomainExceptionエラーが出る。</t>
     <rPh sb="32" eb="33">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氏名は２０文字以内で入力してください</t>
+    <rPh sb="5" eb="9">
+      <t>モジイナイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員情報の登録を完了しました</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加テスト</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21文字以上入力すると、20文字までしか入力できない制限。</t>
+    <rPh sb="2" eb="6">
+      <t>モジイジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -417,7 +454,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +470,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,7 +572,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -542,12 +585,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -557,10 +594,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -573,6 +613,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -593,6 +651,391 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3826212</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{033BA558-F4B9-D418-8DD9-051520794115}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3826212" cy="2247900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>119164</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{273C0ABD-CED1-4F73-AE41-D0E249A5301A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4794250" y="0"/>
+          <a:ext cx="3891064" cy="2286000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428556</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>194073</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D746466-ACE5-4EE1-9FEE-D8293BC93FA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9655106" y="0"/>
+          <a:ext cx="3832294" cy="2251473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>407234</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>166542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83E1F1FE-A62A-43DD-8D38-9E0D0C211580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14433550" y="0"/>
+          <a:ext cx="3785434" cy="2223942"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133047</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>134544</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="矢印: 右 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C0554F8-9922-4F4A-B035-9580321A8DCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8845550" y="1009650"/>
+          <a:ext cx="514047" cy="496494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>418797</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>140894</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="矢印: 右 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26B7BB2F-2966-4012-BE26-4C67CF20B803}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13754100" y="1016000"/>
+          <a:ext cx="514047" cy="496494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>628347</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>140894</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="矢印: 右 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26C9C944-2A32-A2D7-8E66-8E1948E216A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4057650" y="1016000"/>
+          <a:ext cx="514047" cy="496494"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -757,7 +1200,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -922,7 +1365,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1087,7 +1530,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1252,7 +1695,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1527,7 +1970,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1912,7 +2355,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2077,7 +2520,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2559,7 +3002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657F15CF-DB31-4CBD-9D05-5788998812B3}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="28.25" customWidth="1"/>
@@ -2570,88 +3013,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5"/>
+      <c r="D1" s="8"/>
       <c r="E1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>13</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="10">
+        <v>32</v>
+      </c>
+      <c r="I4" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2660,27 +3103,27 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>28</v>
+      <c r="G5" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="10">
+        <v>32</v>
+      </c>
+      <c r="I5" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2689,27 +3132,27 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="10">
+        <v>32</v>
+      </c>
+      <c r="I6" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2718,27 +3161,27 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="10">
+        <v>32</v>
+      </c>
+      <c r="I7" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2747,27 +3190,27 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="10">
+        <v>43</v>
+      </c>
+      <c r="I8" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2776,27 +3219,27 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>24</v>
+      <c r="G9" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="10">
+        <v>32</v>
+      </c>
+      <c r="I9" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2805,27 +3248,27 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>28</v>
+      <c r="G10" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="10">
+        <v>32</v>
+      </c>
+      <c r="I10" s="7">
         <v>46168</v>
       </c>
     </row>
@@ -2834,32 +3277,167 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="7">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="37" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="14"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="14"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="10">
-        <v>46168</v>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="7">
+        <v>46169</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="21">
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="I1:I3"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="C2:C3"/>
@@ -2867,9 +3445,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="H1:H3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2877,17 +3452,37 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAD5B9B-5D72-414C-9EF1-3DA2DA131BE7}">
+  <dimension ref="A13"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="35.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1419303-3149-40D8-86A3-33CE94480919}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5B2FCA-6297-4FFA-90B9-313A9D930BC3}">
   <dimension ref="A12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="42.1640625" customWidth="1"/>
+    <col min="1" max="1" width="51.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
-        <v>39</v>
+      <c r="A12" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2898,16 +3493,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D74BFA-F7B8-4CE1-81C6-F7606FC890B2}">
-  <dimension ref="A13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1419303-3149-40D8-86A3-33CE94480919}">
+  <dimension ref="A12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>6</v>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2918,16 +3513,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECD3C6B-143B-40A2-86BB-ADF3B0459E3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D74BFA-F7B8-4CE1-81C6-F7606FC890B2}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>29</v>
+      <c r="A13" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2938,16 +3533,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4241D5-FA2C-4ECF-AA62-891B742588C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECD3C6B-143B-40A2-86BB-ADF3B0459E3C}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>41</v>
+      <c r="A13" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2958,16 +3553,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B3CB35-8FB3-43B9-AC74-6DAB8D0D4E1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4241D5-FA2C-4ECF-AA62-891B742588C7}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="53.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>44</v>
+      <c r="A13" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2978,15 +3573,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FD0DC8-0710-4D3C-B402-F5A737EEA41D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B3CB35-8FB3-43B9-AC74-6DAB8D0D4E1D}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="37.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2998,16 +3593,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E34E9E-8DF7-491D-87DF-21EAB555F6AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FD0DC8-0710-4D3C-B402-F5A737EEA41D}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="30.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>43</v>
+      <c r="A13" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3018,16 +3613,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAD5B9B-5D72-414C-9EF1-3DA2DA131BE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E34E9E-8DF7-491D-87DF-21EAB555F6AB}">
   <dimension ref="A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="35.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7" t="s">
-        <v>31</v>
+      <c r="A13" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/社員登録テスト項目実施書.xlsx
+++ b/docs/03_test/社員登録テスト項目実施書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC118D8-E075-442F-B4F7-9ED8D01171B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DAE307-557D-4534-A10A-8C7489D2525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E0ED0D0A-EE17-460D-84B3-7BD93845960A}"/>
+    <workbookView xWindow="14303" yWindow="-3953" windowWidth="19394" windowHeight="11476" activeTab="1" xr2:uid="{E0ED0D0A-EE17-460D-84B3-7BD93845960A}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト項目実施" sheetId="1" r:id="rId1"/>
@@ -99,16 +99,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>登録を押す。</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メニューに戻るを押す。</t>
     <rPh sb="5" eb="6">
       <t>モド</t>
@@ -414,20 +404,33 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>21文字以上入力すると、20文字までしか入力できない制限。</t>
-    <rPh sb="2" eb="6">
-      <t>モジイジョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
+    <t>Home画面から登録まで行う。</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21文字入力すると、20文字までしか入力できない制限。</t>
+    <rPh sb="2" eb="4">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="14" eb="16">
+    <rPh sb="12" eb="14">
       <t>モジ</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="18" eb="20">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="26" eb="28">
+    <rPh sb="24" eb="26">
       <t>セイゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -572,7 +575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -597,16 +600,16 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -618,16 +621,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3016,83 +3016,83 @@
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="8" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14"/>
-      <c r="B2" s="8"/>
+      <c r="B2" s="11"/>
       <c r="C2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="E2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="14"/>
-      <c r="B3" s="8"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="7">
         <v>46168</v>
@@ -3106,22 +3106,22 @@
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="7">
         <v>46168</v>
@@ -3132,25 +3132,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="7">
         <v>46168</v>
@@ -3164,22 +3164,22 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="7">
         <v>46168</v>
@@ -3190,25 +3190,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="7">
         <v>46168</v>
@@ -3219,25 +3219,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="7">
         <v>46168</v>
@@ -3248,25 +3248,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="G10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="7">
         <v>46168</v>
@@ -3277,146 +3277,142 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="7">
         <v>46168</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:9" ht="37" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+      <c r="A14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="8" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="14"/>
-      <c r="B16" s="8"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8" t="s">
+      <c r="E16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="14"/>
-      <c r="B17" s="8"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2">
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I18" s="7">
         <v>46169</v>
@@ -3424,11 +3420,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:G17"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="H1:H3"/>
@@ -3445,6 +3436,11 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:G17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3462,7 +3458,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3502,7 +3498,7 @@
   <sheetData>
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3542,7 +3538,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3562,7 +3558,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3582,7 +3578,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3602,7 +3598,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3618,7 @@
   <sheetData>
     <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
